--- a/Examples/Tutorials/RunoffEtc/SoilProps.xlsx
+++ b/Examples/Tutorials/RunoffEtc/SoilProps.xlsx
@@ -5,16 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\aaUnderVC\ApsimX\Examples\Tutorials\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\aaUnderVC\ApsimX\Examples\Tutorials\RunoffEtc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0671D74F-F057-405E-81A9-DA52AA90A526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B696A9-0206-40B4-8803-513D094628CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="15" windowWidth="23010" windowHeight="13890" xr2:uid="{377D550E-A5FB-41FC-A16A-0BF057AA0381}"/>
+    <workbookView minimized="1" xWindow="1335" yWindow="405" windowWidth="26925" windowHeight="19470" xr2:uid="{377D550E-A5FB-41FC-A16A-0BF057AA0381}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1 (2)" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="OLE_LINK12" localSheetId="1">'Sheet1 (2)'!$B$23</definedName>
+  </definedNames>
   <calcPr calcId="191029" iterate="1" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,8 +39,35 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={2FEC07F0-CC45-4873-A3E0-D4A53444B2D0}</author>
+    <author>tc={0CE607E6-1261-4871-AA8C-460156C912AB}</author>
+  </authors>
+  <commentList>
+    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{2FEC07F0-CC45-4873-A3E0-D4A53444B2D0}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Long-term average (Chandra may have the actual tabulated somewhere)</t>
+      </text>
+    </comment>
+    <comment ref="D12" authorId="1" shapeId="0" xr:uid="{0CE607E6-1261-4871-AA8C-460156C912AB}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Average of both catchments over 3-year cropping period)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="56">
   <si>
     <t>mm/day</t>
   </si>
@@ -57,13 +88,284 @@
   </si>
   <si>
     <t>KLClo</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Monaghan, R.M., Paton, R.J., Smith, L.C., Drewry, J.J. and Littlejohn, R.P. 2005.  The impacts of nitrogen fertilisation and increased stocking rate on pasture yield, soil physical condition and nutrient losses in drainage from a cattle-grazed pasture.    </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>New Zealand Journal of Agricultural Research 48:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 227-240</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Monaghan, R.M., Paton, R.J., Smith, L.C. and C. Binet  2000.  Nutrient losses in drainage and surface runoff from a cattle-grazed pasture in Southland.   </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Proceedings of the New Zealand Grassland Association   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>62: 99-104</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Smith, L.C. and Monaghan, R.M.  2003.  Nitrogen and phosphorus losses in overland flow from a cattle-grazed pasture in Southland.    </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>New Zealand Journal of Agricultural Research 46:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 225-238</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Monaghan, R.M., Smith, L.C., Muirhead, R.W., 2016. Pathways of contaminant transfers to water from an artificially-drained soil under intensive grazing by dairy cows. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Agriculture, Ecosystems &amp; Environment</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 220: 76-88.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Monaghan, R.M., Laurenson, S., Dalley, D.E. &amp; Orchiston, T.S. 2017. Grazing strategies for reducing contaminant losses to water from forage crop fields grazed by cattle during winter. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>New Zealand Journal of Agricultural Research</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>60(3):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 333-348.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Ghimire, C. P., Monaghan, R. M., Rutherford, A., Muirhead, R. W., and Lasseur, R. 2024. Grazing strategies for reducing contaminant losses in surface runoff from winter forage crop fields located in hill country and grazed by sheep. New Zealand Journal of Agricultural Research, 1-17. https://doi.org/10.1080/00288233.2024.2336043. </t>
+  </si>
+  <si>
+    <t>Refs:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Surface runoff/surplus rainfall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Surface runoff/annual rainfall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Measured surface runoff</t>
+  </si>
+  <si>
+    <t>nd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Assumed deep drainage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Measured mole-pipe drainage</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Modelled rainfall surplus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Rainfall</t>
+  </si>
+  <si>
+    <t>Mean annual values, mm</t>
+  </si>
+  <si>
+    <t>Internal soil drainage status:</t>
+  </si>
+  <si>
+    <t>Rolling</t>
+  </si>
+  <si>
+    <t>Flat</t>
+  </si>
+  <si>
+    <t>Slope:</t>
+  </si>
+  <si>
+    <t>Pallic (Timaru zl)</t>
+  </si>
+  <si>
+    <t>Pallic (Pukemutu zl)</t>
+  </si>
+  <si>
+    <t>Mix of Brown+Pallics</t>
+  </si>
+  <si>
+    <t>Soil:</t>
+  </si>
+  <si>
+    <t>Sheep-grazed winter crop</t>
+  </si>
+  <si>
+    <t>Cattle-grazed winter crop</t>
+  </si>
+  <si>
+    <t>Cattle-grazed pasture</t>
+  </si>
+  <si>
+    <t>Landuse:</t>
+  </si>
+  <si>
+    <t>Waitahuna</t>
+  </si>
+  <si>
+    <t>Telford</t>
+  </si>
+  <si>
+    <t>Tussock Creek</t>
+  </si>
+  <si>
+    <t>Edendale</t>
+  </si>
+  <si>
+    <t>0-50</t>
+  </si>
+  <si>
+    <t>50-100</t>
+  </si>
+  <si>
+    <t>100-200</t>
+  </si>
+  <si>
+    <t>200-450</t>
+  </si>
+  <si>
+    <t>450-700</t>
+  </si>
+  <si>
+    <t>700-800</t>
+  </si>
+  <si>
+    <t>800-1100</t>
+  </si>
+  <si>
+    <t>1100-1500</t>
+  </si>
+  <si>
+    <t>AD</t>
+  </si>
+  <si>
+    <t>LL</t>
+  </si>
+  <si>
+    <t>DUL</t>
+  </si>
+  <si>
+    <t>BD</t>
+  </si>
+  <si>
+    <t>SAT</t>
+  </si>
+  <si>
+    <t>Mac</t>
+  </si>
+  <si>
+    <t>Depths</t>
+  </si>
+  <si>
+    <t>KS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -71,16 +373,76 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -88,16 +450,75 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="5">
+    <cellStyle name="Good" xfId="2" builtinId="26"/>
+    <cellStyle name="Hyperlink" xfId="4" builtinId="8"/>
+    <cellStyle name="Neutral" xfId="3" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -159,6 +580,61 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5927915" cy="5838825"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="NZLRI_manual.doc [Compatibility Mode] - Word">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69E0FAEE-CEB5-42C1-BF4A-7ED72A7BE6E0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="34084" t="14049" r="21242" b="8224"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="4524375"/>
+          <a:ext cx="5927915" cy="5838825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Ross Monaghan" id="{39A8C758-4FC8-44B9-AF3F-53713933F52D}" userId="S::ross.monaghan@agresearch.co.nz::aa0eb244-c404-4a5c-a506-4fb6f4549f14" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -476,9 +952,20 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="E8" dT="2024-07-03T00:37:00.40" personId="{39A8C758-4FC8-44B9-AF3F-53713933F52D}" id="{2FEC07F0-CC45-4873-A3E0-D4A53444B2D0}">
+    <text>Long-term average (Chandra may have the actual tabulated somewhere)</text>
+  </threadedComment>
+  <threadedComment ref="D12" dT="2024-07-03T00:43:42.94" personId="{39A8C758-4FC8-44B9-AF3F-53713933F52D}" id="{0CE607E6-1261-4871-AA8C-460156C912AB}">
+    <text>Average of both catchments over 3-year cropping period)</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{478A4136-1A17-4636-AD8C-DEF4C0F445F5}">
-  <dimension ref="C6:K49"/>
+  <dimension ref="C6:Z51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="6" spans="3:5" x14ac:dyDescent="0.25">
@@ -624,7 +1111,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C33">
         <v>0</v>
       </c>
@@ -651,8 +1138,32 @@
       <c r="K33">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="S33" t="s">
+        <v>54</v>
+      </c>
+      <c r="T33" t="s">
+        <v>51</v>
+      </c>
+      <c r="U33" t="s">
+        <v>48</v>
+      </c>
+      <c r="V33" t="s">
+        <v>49</v>
+      </c>
+      <c r="W33" t="s">
+        <v>50</v>
+      </c>
+      <c r="X33" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C34">
         <v>50</v>
       </c>
@@ -679,8 +1190,33 @@
       <c r="K34">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="S34" t="s">
+        <v>40</v>
+      </c>
+      <c r="T34">
+        <v>1.21</v>
+      </c>
+      <c r="U34">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="V34">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="W34">
+        <v>0.44700000000000001</v>
+      </c>
+      <c r="X34">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="Y34">
+        <v>426</v>
+      </c>
+      <c r="Z34">
+        <f>X34-W34</f>
+        <v>4.6999999999999986E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C35">
         <v>100</v>
       </c>
@@ -707,8 +1243,33 @@
       <c r="K35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="S35" t="s">
+        <v>41</v>
+      </c>
+      <c r="T35">
+        <v>1.21</v>
+      </c>
+      <c r="U35">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="V35">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="W35">
+        <v>0.44700000000000001</v>
+      </c>
+      <c r="X35">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="Y35">
+        <v>426</v>
+      </c>
+      <c r="Z35">
+        <f t="shared" ref="Z35:Z41" si="4">X35-W35</f>
+        <v>4.6999999999999986E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C36">
         <v>200</v>
       </c>
@@ -735,8 +1296,33 @@
       <c r="K36">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="S36" t="s">
+        <v>42</v>
+      </c>
+      <c r="T36">
+        <v>1.21</v>
+      </c>
+      <c r="U36">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="V36">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="W36">
+        <v>0.44700000000000001</v>
+      </c>
+      <c r="X36">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="Y36">
+        <v>426</v>
+      </c>
+      <c r="Z36">
+        <f t="shared" si="4"/>
+        <v>4.6999999999999986E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C37">
         <v>450</v>
       </c>
@@ -763,8 +1349,33 @@
       <c r="K37">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="S37" t="s">
+        <v>43</v>
+      </c>
+      <c r="T37">
+        <v>1.36</v>
+      </c>
+      <c r="U37">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="V37">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="W37">
+        <v>0.373</v>
+      </c>
+      <c r="X37">
+        <v>0.46100000000000002</v>
+      </c>
+      <c r="Y37">
+        <v>121</v>
+      </c>
+      <c r="Z37">
+        <f t="shared" si="4"/>
+        <v>8.8000000000000023E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C38">
         <v>700</v>
       </c>
@@ -791,8 +1402,33 @@
       <c r="K38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="S38" t="s">
+        <v>44</v>
+      </c>
+      <c r="T38">
+        <v>1.54</v>
+      </c>
+      <c r="U38">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="V38">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="W38">
+        <v>0.377</v>
+      </c>
+      <c r="X38">
+        <v>0.40600000000000003</v>
+      </c>
+      <c r="Y38">
+        <v>44</v>
+      </c>
+      <c r="Z38">
+        <f t="shared" si="4"/>
+        <v>2.9000000000000026E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C39">
         <v>800</v>
       </c>
@@ -819,8 +1455,33 @@
       <c r="K39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="S39" t="s">
+        <v>45</v>
+      </c>
+      <c r="T39">
+        <v>1.62</v>
+      </c>
+      <c r="U39">
+        <v>0.06</v>
+      </c>
+      <c r="V39">
+        <v>0.182</v>
+      </c>
+      <c r="W39">
+        <v>0.36099999999999999</v>
+      </c>
+      <c r="X39">
+        <v>0.379</v>
+      </c>
+      <c r="Y39">
+        <v>21</v>
+      </c>
+      <c r="Z39">
+        <f t="shared" si="4"/>
+        <v>1.8000000000000016E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C40">
         <v>1100</v>
       </c>
@@ -844,32 +1505,257 @@
       <c r="K40">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="S40" t="s">
+        <v>46</v>
+      </c>
+      <c r="T40">
+        <v>1.62</v>
+      </c>
+      <c r="U40">
+        <v>0.06</v>
+      </c>
+      <c r="V40">
+        <v>0.182</v>
+      </c>
+      <c r="W40">
+        <v>0.36099999999999999</v>
+      </c>
+      <c r="X40">
+        <v>0.379</v>
+      </c>
+      <c r="Y40">
+        <v>21</v>
+      </c>
+      <c r="Z40">
+        <f t="shared" si="4"/>
+        <v>1.8000000000000016E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="S41" t="s">
+        <v>47</v>
+      </c>
+      <c r="T41">
+        <v>1.62</v>
+      </c>
+      <c r="U41">
+        <v>6.2E-2</v>
+      </c>
+      <c r="V41">
+        <v>0.187</v>
+      </c>
+      <c r="W41">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="X41">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="Y41">
+        <v>17</v>
+      </c>
+      <c r="Z41">
+        <f t="shared" si="4"/>
+        <v>4.1999999999999982E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="S43" t="s">
+        <v>54</v>
+      </c>
+      <c r="T43" t="s">
+        <v>51</v>
+      </c>
+      <c r="U43" t="s">
+        <v>48</v>
+      </c>
+      <c r="V43" t="s">
+        <v>49</v>
+      </c>
+      <c r="W43" t="s">
+        <v>50</v>
+      </c>
+      <c r="X43" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="3:26" x14ac:dyDescent="0.25">
       <c r="E44">
         <v>46</v>
       </c>
       <c r="G44">
         <v>168</v>
       </c>
-    </row>
-    <row r="45" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="O44" t="s">
+        <v>40</v>
+      </c>
+      <c r="P44">
+        <v>5</v>
+      </c>
+      <c r="Q44">
+        <v>73</v>
+      </c>
+      <c r="R44">
+        <v>21</v>
+      </c>
+      <c r="S44" t="s">
+        <v>40</v>
+      </c>
+      <c r="T44">
+        <v>0.9</v>
+      </c>
+      <c r="U44">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="V44">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="W44">
+        <v>0.44700000000000001</v>
+      </c>
+      <c r="X44">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="Y44">
+        <v>426</v>
+      </c>
+      <c r="Z44">
+        <f>X44-W44</f>
+        <v>0.10300000000000004</v>
+      </c>
+    </row>
+    <row r="45" spans="3:26" x14ac:dyDescent="0.25">
       <c r="E45">
         <v>21</v>
       </c>
       <c r="G45">
         <v>44</v>
       </c>
-    </row>
-    <row r="46" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="O45" t="s">
+        <v>41</v>
+      </c>
+      <c r="P45">
+        <v>5</v>
+      </c>
+      <c r="Q45">
+        <v>73</v>
+      </c>
+      <c r="R45">
+        <v>21</v>
+      </c>
+      <c r="S45" t="s">
+        <v>41</v>
+      </c>
+      <c r="T45">
+        <v>0.9</v>
+      </c>
+      <c r="U45">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="V45">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="W45">
+        <v>0.44700000000000001</v>
+      </c>
+      <c r="X45">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="Y45">
+        <v>426</v>
+      </c>
+      <c r="Z45">
+        <f t="shared" ref="Z45:Z51" si="5">X45-W45</f>
+        <v>0.10300000000000004</v>
+      </c>
+    </row>
+    <row r="46" spans="3:26" x14ac:dyDescent="0.25">
       <c r="E46">
         <v>22</v>
       </c>
       <c r="G46">
         <v>12</v>
       </c>
-    </row>
-    <row r="48" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="O46" t="s">
+        <v>42</v>
+      </c>
+      <c r="P46">
+        <v>5</v>
+      </c>
+      <c r="Q46">
+        <v>73</v>
+      </c>
+      <c r="R46">
+        <v>21</v>
+      </c>
+      <c r="S46" t="s">
+        <v>42</v>
+      </c>
+      <c r="T46">
+        <v>1.21</v>
+      </c>
+      <c r="U46">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="V46">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="W46">
+        <v>0.44700000000000001</v>
+      </c>
+      <c r="X46">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="Y46">
+        <v>426</v>
+      </c>
+      <c r="Z46">
+        <f t="shared" si="5"/>
+        <v>4.6999999999999986E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="O47" t="s">
+        <v>43</v>
+      </c>
+      <c r="P47">
+        <v>5</v>
+      </c>
+      <c r="Q47">
+        <v>76</v>
+      </c>
+      <c r="R47">
+        <v>18</v>
+      </c>
+      <c r="S47" t="s">
+        <v>43</v>
+      </c>
+      <c r="T47">
+        <v>1.36</v>
+      </c>
+      <c r="U47">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="V47">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="W47">
+        <v>0.373</v>
+      </c>
+      <c r="X47">
+        <v>0.46100000000000002</v>
+      </c>
+      <c r="Y47">
+        <v>121</v>
+      </c>
+      <c r="Z47">
+        <f t="shared" si="5"/>
+        <v>8.8000000000000023E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="3:26" x14ac:dyDescent="0.25">
       <c r="E48">
         <f>E44+E45/60+E46/60/60</f>
         <v>46.356111111111112</v>
@@ -878,8 +1764,45 @@
         <f>G44+G45/60+G46/60/60</f>
         <v>168.73666666666665</v>
       </c>
-    </row>
-    <row r="49" spans="5:7" x14ac:dyDescent="0.25">
+      <c r="O48" t="s">
+        <v>44</v>
+      </c>
+      <c r="P48">
+        <v>5</v>
+      </c>
+      <c r="Q48">
+        <v>73</v>
+      </c>
+      <c r="R48">
+        <v>21</v>
+      </c>
+      <c r="S48" t="s">
+        <v>44</v>
+      </c>
+      <c r="T48">
+        <v>1.54</v>
+      </c>
+      <c r="U48">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="V48">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="W48">
+        <v>0.377</v>
+      </c>
+      <c r="X48">
+        <v>0.40600000000000003</v>
+      </c>
+      <c r="Y48">
+        <v>44</v>
+      </c>
+      <c r="Z48">
+        <f t="shared" si="5"/>
+        <v>2.9000000000000026E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="5:26" x14ac:dyDescent="0.25">
       <c r="E49">
         <f>ROUND(E48,3)</f>
         <v>46.356000000000002</v>
@@ -887,10 +1810,410 @@
       <c r="G49">
         <f>ROUND(G48,3)</f>
         <v>168.73699999999999</v>
+      </c>
+      <c r="O49" t="s">
+        <v>45</v>
+      </c>
+      <c r="P49">
+        <v>6</v>
+      </c>
+      <c r="Q49">
+        <v>78</v>
+      </c>
+      <c r="R49">
+        <v>15</v>
+      </c>
+      <c r="S49" t="s">
+        <v>45</v>
+      </c>
+      <c r="T49">
+        <v>1.62</v>
+      </c>
+      <c r="U49">
+        <v>0.06</v>
+      </c>
+      <c r="V49">
+        <v>0.182</v>
+      </c>
+      <c r="W49">
+        <v>0.36099999999999999</v>
+      </c>
+      <c r="X49">
+        <v>0.379</v>
+      </c>
+      <c r="Y49">
+        <v>21</v>
+      </c>
+      <c r="Z49">
+        <f t="shared" si="5"/>
+        <v>1.8000000000000016E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="5:26" x14ac:dyDescent="0.25">
+      <c r="O50" t="s">
+        <v>46</v>
+      </c>
+      <c r="P50">
+        <v>6</v>
+      </c>
+      <c r="Q50">
+        <v>78</v>
+      </c>
+      <c r="R50">
+        <v>15</v>
+      </c>
+      <c r="S50" t="s">
+        <v>46</v>
+      </c>
+      <c r="T50">
+        <v>1.62</v>
+      </c>
+      <c r="U50">
+        <v>0.06</v>
+      </c>
+      <c r="V50">
+        <v>0.182</v>
+      </c>
+      <c r="W50">
+        <v>0.36099999999999999</v>
+      </c>
+      <c r="X50">
+        <v>0.379</v>
+      </c>
+      <c r="Y50">
+        <v>21</v>
+      </c>
+      <c r="Z50">
+        <f t="shared" si="5"/>
+        <v>1.8000000000000016E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="5:26" x14ac:dyDescent="0.25">
+      <c r="O51" t="s">
+        <v>47</v>
+      </c>
+      <c r="P51">
+        <v>6</v>
+      </c>
+      <c r="Q51">
+        <v>78</v>
+      </c>
+      <c r="R51">
+        <v>15</v>
+      </c>
+      <c r="S51" t="s">
+        <v>47</v>
+      </c>
+      <c r="T51">
+        <v>1.62</v>
+      </c>
+      <c r="U51">
+        <v>6.2E-2</v>
+      </c>
+      <c r="V51">
+        <v>0.187</v>
+      </c>
+      <c r="W51">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="X51">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="Y51">
+        <v>17</v>
+      </c>
+      <c r="Z51">
+        <f t="shared" si="5"/>
+        <v>4.1999999999999982E-2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{040C0E76-8E09-4B11-8EB7-596FB1480B8C}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="32.42578125" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="10" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="10" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="13">
+        <v>4</v>
+      </c>
+      <c r="C5" s="13">
+        <v>3</v>
+      </c>
+      <c r="D5" s="12">
+        <v>3</v>
+      </c>
+      <c r="E5" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="7">
+        <v>911</v>
+      </c>
+      <c r="C8" s="6">
+        <f>AVERAGE(1064,1153,928)</f>
+        <v>1048.3333333333333</v>
+      </c>
+      <c r="D8" s="6">
+        <f>AVERAGE(688,637,670)</f>
+        <v>665</v>
+      </c>
+      <c r="E8" s="7">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="7">
+        <v>370</v>
+      </c>
+      <c r="C9" s="6">
+        <f>AVERAGE(349,426,268)</f>
+        <v>347.66666666666669</v>
+      </c>
+      <c r="D9" s="6">
+        <f>AVERAGE(122,151,148)</f>
+        <v>140.33333333333334</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="7">
+        <v>210</v>
+      </c>
+      <c r="C10" s="6">
+        <f>AVERAGE(215,225,207)</f>
+        <v>215.66666666666666</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B9-B10-B12</f>
+        <v>157</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C9-C10-C12</f>
+        <v>46.000000000000028</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="9">
+        <v>3</v>
+      </c>
+      <c r="C12" s="8">
+        <f>AVERAGE(127,45)</f>
+        <v>86</v>
+      </c>
+      <c r="D12" s="8">
+        <f>(AVERAGE(92,105))/3</f>
+        <v>32.833333333333336</v>
+      </c>
+      <c r="E12" s="8">
+        <f>AVERAGE(6,28,4)</f>
+        <v>12.666666666666666</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B13" s="7"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="5">
+        <f>B$12/B8</f>
+        <v>3.2930845225027441E-3</v>
+      </c>
+      <c r="C14" s="5">
+        <f>C$12/C8</f>
+        <v>8.2034976152623215E-2</v>
+      </c>
+      <c r="D14" s="5">
+        <f>D$12/D8</f>
+        <v>4.9373433583959903E-2</v>
+      </c>
+      <c r="E14" s="5">
+        <f>E$12/E8</f>
+        <v>1.4901960784313726E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5">
+        <f>B$12/B9</f>
+        <v>8.1081081081081086E-3</v>
+      </c>
+      <c r="C15" s="5">
+        <f>C$12/C9</f>
+        <v>0.24736337488015339</v>
+      </c>
+      <c r="D15" s="5">
+        <f>D$12/D9</f>
+        <v>0.23396674584323041</v>
+      </c>
+      <c r="E15" s="5" t="e">
+        <f>E$12/E9</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D19" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C20" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E18" r:id="rId1" display="https://doi.org/10.1080/00288233.2024.2336043" xr:uid="{C994E477-DCAA-4098-8B81-98DA6EBA3449}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
 </file>